--- a/Phieu_trai_nghiem_Viet_Anh_Class.xlsx
+++ b/Phieu_trai_nghiem_Viet_Anh_Class.xlsx
@@ -819,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -891,106 +891,106 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Mật khẩu</t>
+          <t>Cách đăng nhập</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Bạn KHÔNG cần mật khẩu. Ở trang đăng nhập, kéo xuống khối “Demo” và bấm đúng nút mang tên bạn.</t>
+          <t>Ở trang đăng nhập có hai ô “Email” và “Mật khẩu”. Gõ tay email của vai bạn đang đóng (xem bảng bên dưới), mật khẩu là demo1234, rồi bấm nút vàng “Đăng nhập”.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr"/>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Quan trọng nhất</t>
+          <t>Mật khẩu chung</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cột GHI CHÚ mới là thứ chúng tôi cần. Các ô chọn nhanh chỉ để thống kê. Đừng ngại viết dài, viết thẳng, chê thoải mái.</t>
+          <t>demo1234 — dùng chung cho cả 9 tài khoản.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Đổi vai</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Bấm tên mình ở góc trên bên phải → “Đăng xuất”, rồi đăng nhập lại bằng email của vai kế tiếp.</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Quan trọng nhất</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Cột GHI CHÚ mới là thứ chúng tôi cần. Các ô chọn nhanh chỉ để thống kê. Đừng ngại viết dài, viết thẳng, chê thoải mái.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>CÁCH ĐIỀN — VÀ CÁCH DÙNG LẠI CHO NHIỀU VÒNG</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Ô tô vàng nhạt</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Là ô bạn cần điền. Ô trắng là phần mô tả sẵn, bạn không phải sửa.</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Cột “Đúng như mô tả?”</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Chọn từ danh sách sổ xuống. Nếu app khác mô tả, hãy nói rõ khác chỗ nào ở cột ghi chú.</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Cột “Dễ dùng”</t>
+          <t>Ô tô vàng nhạt</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>1 = rất khó dùng · 5 = rất dễ. Chấm theo cảm giác thật, không cần cân nhắc nhiều.</t>
+          <t>Là ô bạn cần điền. Ô trắng là phần mô tả sẵn, bạn không phải sửa.</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr"/>
     </row>
-    <row r="15" ht="34" customHeight="1">
+    <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>VÒNG 1 / 2 / 3</t>
+          <t>Cột “Đúng như mô tả?”</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mỗi vòng thử có một nhóm cột riêng. Vòng 1 điền trước. Sau khi đội kỹ thuật sửa, bạn quay lại điền cột “Đã sửa?” rồi thử lại và điền vòng 2. Cứ thế cho tới khi hết lỗi.</t>
+          <t>Chọn từ danh sách sổ xuống. Nếu app khác mô tả, hãy nói rõ khác chỗ nào ở cột ghi chú.</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="inlineStr"/>
     </row>
-    <row r="16" ht="34" customHeight="1">
+    <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Cần hơn 3 vòng?</t>
+          <t>Cột “Dễ dùng”</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Bôi đen nhóm cột của Vòng 3 (từ cột “Đã sửa?” tới “Ghi chú”), sao chép và dán sang phải. Sổ lỗi ở sheet SỔ LỖI thì không giới hạn số vòng.</t>
+          <t>1 = rất khó dùng · 5 = rất dễ. Chấm theo cảm giác thật, không cần cân nhắc nhiều.</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -999,123 +999,111 @@
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Sheet SỔ LỖI</t>
+          <t>VÒNG 1 / 2 / 3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Mỗi lỗi bạn gặp ghi MỘT dòng ở đó, rồi theo dõi tới khi nó được sửa xong. Đây là chỗ theo dõi xuyên suốt mọi vòng.</t>
+          <t>Mỗi vòng thử có một nhóm cột riêng. Vòng 1 điền trước. Sau khi đội kỹ thuật sửa, bạn quay lại điền cột “Đã sửa?” rồi thử lại và điền vòng 2. Cứ thế cho tới khi hết lỗi.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="inlineStr"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Cần hơn 3 vòng?</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Bôi đen nhóm cột của Vòng 3 (từ cột “Đã sửa?” tới “Ghi chú”), sao chép và dán sang phải. Sổ lỗi ở sheet SỔ LỖI thì không giới hạn số vòng.</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Sheet SỔ LỖI</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Mỗi lỗi bạn gặp ghi MỘT dòng ở đó, rồi theo dõi tới khi nó được sửa xong. Đây là chỗ theo dõi xuyên suốt mọi vòng.</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>TÀI KHOẢN CỦA TỪNG NGƯỜI</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Người thử</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Vai — bấm nút demo tương ứng</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Tài khoản</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Vai bạn đóng</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Email đăng nhập (gõ tay vào ô Email)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Gắn với ai / lớp nào</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>N1 · Giáo viên</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Giáo viên chủ nhiệm</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>test1.gvcn@truongvietanh.com</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Chủ nhiệm lớp 7B1 · cơ sở Việt Anh Quận 2</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr"/>
-      <c r="B22" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Học sinh (tổ trưởng)</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>test1.hs@student.truongvietanh.com</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Học lớp 7B1 · được giao làm tổ trưởng điểm danh</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr"/>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Phụ huynh</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>test1.ph@truongvietanh.com</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Là phụ huynh của chính học sinh ở trên</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>N2 · Ban giám hiệu</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Ban giám hiệu</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>test2.bgh@truongvietanh.com</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Phụ trách cơ sở Việt Anh Quận 2</t>
         </is>
       </c>
     </row>
@@ -1123,57 +1111,57 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="7" t="inlineStr">
         <is>
+          <t>Phụ huynh</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>test1.ph@truongvietanh.com</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Là phụ huynh của chính học sinh ở trên</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>N2 · Ban giám hiệu</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Ban giám hiệu</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>test2.bgh@truongvietanh.com</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Phụ trách cơ sở Việt Anh Quận 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
           <t>Học sinh (thường)</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>test2.hs@student.truongvietanh.com</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Học lớp 7B1 · KHÔNG phải tổ trưởng</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr"/>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Phụ huynh</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>test2.ph@truongvietanh.com</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Là phụ huynh của chính học sinh ở trên</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>N3 · Quản trị viên</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Quản trị viên</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>test3.admin@truongvietanh.com</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Thấy toàn bộ hệ thống, mọi cơ sở</t>
         </is>
       </c>
     </row>
@@ -1181,123 +1169,163 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="7" t="inlineStr">
         <is>
+          <t>Phụ huynh</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>test2.ph@truongvietanh.com</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Là phụ huynh của chính học sinh ở trên</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>N3 · Quản trị viên</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Quản trị viên</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>test3.admin@truongvietanh.com</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Thấy toàn bộ hệ thống, mọi cơ sở</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
           <t>Giáo viên chủ nhiệm</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>test3.gvcn@truongvietanh.com</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Chủ nhiệm lớp 6A2 · cơ sở Việt Anh Gò Vấp</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr"/>
-      <c r="B29" s="7" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr"/>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Học sinh</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>test3.hs@student.truongvietanh.com</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Học lớp 6A2 · cơ sở Việt Anh Gò Vấp</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>AI LIÊN QUAN TỚI AI — dùng cho phần phối hợp</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>CƠ SỞ VIỆT ANH QUẬN 2  →  lớp 7B1  →  giáo viên chủ nhiệm = Người 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        trong lớp 7B1 có:  học sinh của Người 1 (tổ trưởng điểm danh)  +  học sinh của Người 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        phụ huynh của Người 1 ── là cha/mẹ của ──&gt; học sinh Người 1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">        phụ huynh của Người 2 ── là cha/mẹ của ──&gt; học sinh Người 2</t>
+          <t xml:space="preserve">        trong lớp 7B1 có:  học sinh của Người 1 (tổ trưởng điểm danh)  +  học sinh của Người 2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">        phụ huynh của Người 1 ── là cha/mẹ của ──&gt; học sinh Người 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        phụ huynh của Người 2 ── là cha/mẹ của ──&gt; học sinh Người 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">        ban giám hiệu cơ sở này = Người 2  (thấy 7B1, KHÔNG thấy lớp nào của Gò Vấp)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>CƠ SỞ VIỆT ANH GÒ VẤP  →  lớp 6A2  →  giáo viên chủ nhiệm = Người 3</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">        trong lớp 6A2 có: học sinh của Người 3</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">        (cơ sở này còn lớp 6A1 của tài khoản demo cũ — không thuộc phần thử)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>QUẢN TRỊ VIÊN = Người 3  →  thấy TẤT CẢ mọi cơ sở, mọi lớp. Là người đối chứng.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>KHI NÀO PHẢI DỪNG NGAY</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="46" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="47" ht="46" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Nếu bạn nhìn thấy dữ liệu của học sinh KHÔNG thuộc phạm vi mình — con của phụ huynh khác, lớp của giáo viên khác, cơ sở khác — thì DỪNG ĐỢT THỬ, chụp màn hình, và báo ngay. Đây là lỗi nghiêm trọng nhất, quan trọng hơn mọi lỗi giao diện.</t>
         </is>
@@ -1308,22 +1336,22 @@
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2101,11 +2129,11 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>◆  VAI: GIÁO VIÊN CHỦ NHIỆM lớp 7B1        —        Nút demo: “N1 · Giáo viên chủ nhiệm 7B1”        —        Đây là vai chính của bạn. Hãy đi chậm và ghi lại mọi chỗ thấy khó hiểu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
+          <t>◆  VAI: GIÁO VIÊN CHỦ NHIỆM lớp 7B1        —        Đăng nhập: test1.gvcn@truongvietanh.com   ·   mật khẩu: demo1234        —        Đây là vai chính của bạn. Hãy đi chậm và ghi lại mọi chỗ thấy khó hiểu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
       <c r="A11" s="7" t="n">
         <v>1</v>
       </c>
@@ -2116,7 +2144,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Trang đăng nhập: nền có đám đông học sinh mặc đồng phục đi lại, giữa trang là dòng chữ lớn “Viet Anh Class”, bên dưới có nút trắng “Đăng nhập với Google” và một dòng chữ nhỏ “Dành cho phụ huynh”.</t>
+          <t>Trang đăng nhập: nền có đám đông học sinh mặc đồng phục đi lại, giữa trang là dòng chữ lớn “Viet Anh Class”. Trong thẻ đăng nhập có: nút trắng “Đăng nhập với Google”, bên dưới là hai ô “Email” và “Mật khẩu” kèm nút vàng “Đăng nhập”, dưới cùng là dòng chữ nhỏ “Dành cho phụ huynh”.</t>
         </is>
       </c>
       <c r="D11" s="23" t="n"/>
@@ -2135,18 +2163,18 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="39" customHeight="1">
       <c r="A12" s="7" t="n">
         <v>2</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Kéo xuống dưới thẻ đăng nhập, tìm khối chữ “Demo”. Bấm nút “N1 · Giáo viên chủ nhiệm 7B1”.</t>
+          <t>Gõ vào ô “Email”: test1.gvcn@truongvietanh.com — ô “Mật khẩu”: demo1234 — rồi bấm nút vàng “Đăng nhập”.</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>App vào thẳng, không hỏi mật khẩu. Hiện ra thanh menu màu xanh đậm ở trên cùng.</t>
+          <t>App đưa bạn vào thẳng trang làm việc. Hiện ra thanh menu màu xanh đậm ở trên cùng.</t>
         </is>
       </c>
       <c r="D12" s="23" t="n"/>
@@ -2651,7 +2679,7 @@
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>📱 TRÊN ĐIỆN THOẠI — Lấy điện thoại, mở https://class.vietanh.org, đăng nhập cùng nút demo, rồi làm lại việc điểm danh.</t>
+          <t>📱 TRÊN ĐIỆN THOẠI — Lấy điện thoại, mở https://class.vietanh.org, đăng nhập bằng cùng email và mật khẩu, rồi làm lại việc điểm danh.</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
@@ -2708,7 +2736,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>◆  VAI: HỌC SINH — kiêm TỔ TRƯỞNG ĐIỂM DANH lớp 7B1        —        Nút demo: “N1 · Học sinh 7B1 (tổ trưởng)”        —        Giờ bạn nhìn app bằng mắt của một em học sinh được giao thêm việc điểm danh hộ lớp.</t>
+          <t>◆  VAI: HỌC SINH — kiêm TỔ TRƯỞNG ĐIỂM DANH lớp 7B1        —        Đăng nhập: test1.hs@student.truongvietanh.com   ·   mật khẩu: demo1234        —        Giờ bạn nhìn app bằng mắt của một em học sinh được giao thêm việc điểm danh hộ lớp.</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2746,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Đăng nhập bằng nút demo “N1 · Học sinh 7B1 (tổ trưởng)”.</t>
+          <t>Đăng nhập bằng email test1.hs@student.truongvietanh.com và mật khẩu demo1234.</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -2895,7 +2923,7 @@
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>◆  VAI: PHỤ HUYNH        —        Nút demo: “N1 · Phụ huynh”        —        Cuối cùng, bạn nhìn app bằng mắt một người cha/mẹ ở nhà.</t>
+          <t>◆  VAI: PHỤ HUYNH        —        Đăng nhập: test1.ph@truongvietanh.com   ·   mật khẩu: demo1234        —        Cuối cùng, bạn nhìn app bằng mắt một người cha/mẹ ở nhà.</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2933,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Đăng xuất, rồi đăng nhập bằng nút demo “N1 · Phụ huynh”.</t>
+          <t>Đăng xuất, rồi đăng nhập bằng email test1.ph@truongvietanh.com và mật khẩu demo1234.</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -3589,17 +3617,17 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>◆  VAI: BAN GIÁM HIỆU — cơ sở Việt Anh Quận 2        —        Nút demo: “N2 · Ban giám hiệu Quận 2”        —        Vai chính của bạn. Bạn nhìn app ở tầm cả cơ sở, không phải một lớp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t>◆  VAI: BAN GIÁM HIỆU — cơ sở Việt Anh Quận 2        —        Đăng nhập: test2.bgh@truongvietanh.com   ·   mật khẩu: demo1234        —        Vai chính của bạn. Bạn nhìn app ở tầm cả cơ sở, không phải một lớp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39" customHeight="1">
       <c r="A11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Mở https://class.vietanh.org, bấm nút demo “N2 · Ban giám hiệu Quận 2”.</t>
+          <t>Mở https://class.vietanh.org, nhập email test2.bgh@truongvietanh.com và mật khẩu demo1234 rồi bấm “Đăng nhập”.</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -4046,7 +4074,7 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>◆  VAI: HỌC SINH THƯỜNG lớp 7B1        —        Nút demo: “N2 · Học sinh 7B1”        —        Em này học CÙNG LỚP với học sinh của Người thử 1, nhưng KHÔNG phải tổ trưởng.</t>
+          <t>◆  VAI: HỌC SINH THƯỜNG lớp 7B1        —        Đăng nhập: test2.hs@student.truongvietanh.com   ·   mật khẩu: demo1234        —        Em này học CÙNG LỚP với học sinh của Người thử 1, nhưng KHÔNG phải tổ trưởng.</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4084,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Đăng xuất, đăng nhập bằng nút demo “N2 · Học sinh 7B1”.</t>
+          <t>Đăng xuất, đăng nhập bằng email test2.hs@student.truongvietanh.com và mật khẩu demo1234.</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -4203,7 +4231,7 @@
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>◆  VAI: PHỤ HUYNH        —        Nút demo: “N2 · Phụ huynh”        —        Bạn là phụ huynh của em học sinh vừa rồi.</t>
+          <t>◆  VAI: PHỤ HUYNH        —        Đăng nhập: test2.ph@truongvietanh.com   ·   mật khẩu: demo1234        —        Bạn là phụ huynh của em học sinh vừa rồi.</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4241,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Đăng xuất, đăng nhập bằng nút demo “N2 · Phụ huynh”.</t>
+          <t>Đăng xuất, đăng nhập bằng email test2.ph@truongvietanh.com và mật khẩu demo1234.</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -4897,17 +4925,17 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>◆  VAI: QUẢN TRỊ VIÊN        —        Nút demo: “N3 · Quản trị viên”        —        Vai chính của bạn — người thấy toàn hệ thống. Bạn cũng là người đối chứng cho hai bạn kia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t>◆  VAI: QUẢN TRỊ VIÊN        —        Đăng nhập: test3.admin@truongvietanh.com   ·   mật khẩu: demo1234        —        Vai chính của bạn — người thấy toàn hệ thống. Bạn cũng là người đối chứng cho hai bạn kia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="39" customHeight="1">
       <c r="A11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Mở https://class.vietanh.org, bấm nút demo “N3 · Quản trị viên”.</t>
+          <t>Mở https://class.vietanh.org, nhập email test3.admin@truongvietanh.com và mật khẩu demo1234 rồi bấm “Đăng nhập”.</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -5324,7 +5352,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>◆  VAI: GIÁO VIÊN CHỦ NHIỆM lớp 6A2 — cơ sở Việt Anh Gò Vấp        —        Nút demo: “N3 · Giáo viên chủ nhiệm 6A2”        —        Lớp này ở cơ sở KHÁC với lớp của Người thử 1. Đây là vế đối chứng cho các phép thử ranh giới.</t>
+          <t>◆  VAI: GIÁO VIÊN CHỦ NHIỆM lớp 6A2 — cơ sở Việt Anh Gò Vấp        —        Đăng nhập: test3.gvcn@truongvietanh.com   ·   mật khẩu: demo1234        —        Lớp này ở cơ sở KHÁC với lớp của Người thử 1. Đây là vế đối chứng cho các phép thử ranh giới.</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5362,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Đăng xuất, đăng nhập bằng nút demo “N3 · Giáo viên chủ nhiệm 6A2”.</t>
+          <t>Đăng xuất, đăng nhập bằng email test3.gvcn@truongvietanh.com và mật khẩu demo1234.</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -5481,7 +5509,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>◆  VAI: HỌC SINH lớp 6A2        —        Nút demo: “N3 · Học sinh 6A2”        —        Em học sinh ở cơ sở Gò Vấp.</t>
+          <t>◆  VAI: HỌC SINH lớp 6A2        —        Đăng nhập: test3.hs@student.truongvietanh.com   ·   mật khẩu: demo1234        —        Em học sinh ở cơ sở Gò Vấp.</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5519,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Đăng xuất, đăng nhập bằng nút demo “N3 · Học sinh 6A2”.</t>
+          <t>Đăng xuất, đăng nhập bằng email test3.hs@student.truongvietanh.com và mật khẩu demo1234.</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
